--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487012_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487012_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4201</v>
+        <v>5.2667</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1117</v>
+        <v>3.6619</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3084</v>
+        <v>1.6049</v>
       </c>
       <c r="G2" t="n">
         <v>5.0168</v>
@@ -610,13 +610,13 @@
         <v>1.2321</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.108</v>
+        <v>-0.2615</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0462</v>
+        <v>-0.4961</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0618</v>
+        <v>0.2346</v>
       </c>
       <c r="V2" t="n">
         <v>-0.7207</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SANCHEZ PERDIGUERO</t>
+          <t>A. IKPEZE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0797</v>
+        <v>4.2689</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2012</v>
+        <v>1.8459</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8785</v>
+        <v>2.423</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4238</v>
+        <v>3.8774</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3104</v>
+        <v>2.7087</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8866000000000001</v>
+        <v>1.1686</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0124</v>
+        <v>2.3265</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2492</v>
+        <v>2.0897</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.2368</v>
+        <v>0.2368</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4114</v>
+        <v>1.5509</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0612</v>
+        <v>0.6191</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3502</v>
+        <v>0.9318</v>
       </c>
       <c r="P3" t="n">
         <v>0.616</v>
@@ -688,28 +688,28 @@
         <v>1.6427</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3192</v>
+        <v>0.4737</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6037</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7155</v>
+        <v>0.408</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7207</v>
+        <v>-0.6982</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6119</v>
+        <v>0.4805</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1088</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. IKPEZE</t>
+          <t>A. SANCHEZ PERDIGUERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8391</v>
+        <v>2.5412</v>
       </c>
       <c r="E4" t="n">
-        <v>1.505</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3341</v>
+        <v>2.4635</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8774</v>
+        <v>0.4238</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7087</v>
+        <v>1.3104</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1686</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3265</v>
+        <v>0.0124</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0897</v>
+        <v>1.2492</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2368</v>
+        <v>-1.2368</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5509</v>
+        <v>0.4114</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6191</v>
+        <v>0.0612</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9318</v>
+        <v>0.3502</v>
       </c>
       <c r="P4" t="n">
         <v>0.616</v>
@@ -766,22 +766,22 @@
         <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0438</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2753</v>
+        <v>0.4802</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3191</v>
+        <v>0.3005</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6982</v>
+        <v>0.7207</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4805</v>
+        <v>0.6119</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1786</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5507</v>
+        <v>2.1932</v>
       </c>
       <c r="E5" t="n">
-        <v>1.069</v>
+        <v>0.8598</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4816</v>
+        <v>1.3334</v>
       </c>
       <c r="G5" t="n">
         <v>4.3077</v>
@@ -844,13 +844,13 @@
         <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1178</v>
+        <v>0.7604</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4879</v>
+        <v>0.2787</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6298</v>
+        <v>0.4816</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0633</v>
+        <v>1.2247</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5175</v>
+        <v>-0.3857</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5808</v>
+        <v>1.6104</v>
       </c>
       <c r="G6" t="n">
         <v>-1.4984</v>
@@ -922,13 +922,13 @@
         <v>1.8481</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3646</v>
+        <v>0.526</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2245</v>
+        <v>0.3562</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1401</v>
+        <v>0.1698</v>
       </c>
       <c r="V6" t="n">
         <v>0.3491</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7665</v>
+        <v>-0.3481</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0102</v>
+        <v>0.4286</v>
       </c>
       <c r="F7" t="n">
         <v>-0.7766999999999999</v>
@@ -1000,10 +1000,10 @@
         <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>0.124</v>
+        <v>0.5424</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6433</v>
+        <v>-0.2249</v>
       </c>
       <c r="U7" t="n">
         <v>0.7673</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PRIOR RUIZ</t>
+          <t>M. FALL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4</v>
+        <v>-1.2819</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0267</v>
+        <v>-1.081</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3733</v>
+        <v>-0.2009</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8997</v>
+        <v>-0.2261</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8077</v>
+        <v>-0.1104</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.092</v>
+        <v>-0.1157</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3947</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6974</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6974</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.505</v>
+        <v>-0.2261</v>
       </c>
       <c r="N8" t="n">
         <v>-0.1104</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3947</v>
+        <v>-0.1157</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4107</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4107</v>
+        <v>0.2053</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0891</v>
+        <v>-0.2344</v>
       </c>
       <c r="T8" t="n">
-        <v>0.368</v>
+        <v>-0.0543</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2789</v>
+        <v>-0.1801</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. FALL</t>
+          <t>A. PRIOR RUIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5504</v>
+        <v>-1.6092</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2902</v>
+        <v>-1.2359</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2602</v>
+        <v>-0.3733</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2261</v>
+        <v>-1.8997</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1104</v>
+        <v>-0.8077</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1157</v>
+        <v>-1.092</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-1.3947</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.6974</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.6974</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2261</v>
+        <v>-0.505</v>
       </c>
       <c r="N9" t="n">
         <v>-0.1104</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1157</v>
+        <v>-0.3947</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2053</v>
+        <v>0.4107</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5029</v>
+        <v>-0.1202</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2635</v>
+        <v>0.1588</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2394</v>
+        <v>-0.2789</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8183</v>
+        <v>-1.6527</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0952</v>
+        <v>-0.7813</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7231</v>
+        <v>-0.8713</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8435</v>
@@ -1234,13 +1234,13 @@
         <v>0.616</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5908</v>
+        <v>-0.4252</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6587</v>
+        <v>-0.3449</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0679</v>
+        <v>-0.0803</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6308</v>
+        <v>-3.1573</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.4127</v>
+        <v>-5.1764</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7819</v>
+        <v>2.019</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7823</v>
@@ -1312,13 +1312,13 @@
         <v>1.8481</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1967</v>
+        <v>0.6702</v>
       </c>
       <c r="T11" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.3213</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1117</v>
+        <v>0.3489</v>
       </c>
       <c r="V11" t="n">
         <v>0.2402</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.7869</v>
+        <v>7.4455</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.445200000000001</v>
+        <v>-1.7863</v>
       </c>
       <c r="F12" t="n">
         <v>9.231999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>7.287999999999999</v>
+        <v>7.287999999999998</v>
       </c>
       <c r="H12" t="n">
         <v>5.4333</v>
@@ -1390,13 +1390,13 @@
         <v>11.2938</v>
       </c>
       <c r="S12" t="n">
-        <v>2.0535</v>
+        <v>2.7121</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1179</v>
+        <v>0.5407</v>
       </c>
       <c r="U12" t="n">
-        <v>2.1713</v>
+        <v>2.1714</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5278</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.881</v>
+        <v>4.4252</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8195</v>
+        <v>2.6688</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0615</v>
+        <v>1.7564</v>
       </c>
       <c r="G13" t="n">
         <v>2.4184</v>
@@ -1468,13 +1468,13 @@
         <v>0.8214</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4893</v>
+        <v>1.0335</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3016</v>
+        <v>0.151</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1877</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.1786</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0979</v>
+        <v>2.5042</v>
       </c>
       <c r="E14" t="n">
         <v>4.2624</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.1645</v>
+        <v>-1.7583</v>
       </c>
       <c r="G14" t="n">
         <v>3.0045</v>
@@ -1546,13 +1546,13 @@
         <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3604</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>-0.2753</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0851</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>1.0698</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8976</v>
+        <v>1.8618</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6924</v>
+        <v>1.1108</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2052</v>
+        <v>0.7509</v>
       </c>
       <c r="G15" t="n">
         <v>0.8248</v>
@@ -1624,13 +1624,13 @@
         <v>1.8481</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9806</v>
+        <v>-0.0165</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.1204</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4418</v>
+        <v>0.1039</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5893</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3929</v>
+        <v>1.3134</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.7036</v>
+        <v>-1.1806</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0965</v>
+        <v>2.4941</v>
       </c>
       <c r="G16" t="n">
         <v>0.9837</v>
@@ -1702,13 +1702,13 @@
         <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3157</v>
+        <v>-0.3951</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3174</v>
+        <v>-0.7944</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0018</v>
+        <v>0.3993</v>
       </c>
       <c r="V16" t="n">
         <v>0.1088</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1816</v>
+        <v>0.5053</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3529</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1713</v>
+        <v>1.2306</v>
       </c>
       <c r="G17" t="n">
         <v>-0.659</v>
@@ -1780,13 +1780,13 @@
         <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2003</v>
+        <v>-0.5134</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3174</v>
+        <v>-0.6898</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1172</v>
+        <v>0.1765</v>
       </c>
       <c r="V17" t="n">
         <v>0.2402</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. TEJERA TEJO</t>
+          <t>M. ALVAREZ PUERTAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5933</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1846</v>
+        <v>-0.672</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4087</v>
+        <v>0.1019</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4576</v>
+        <v>-0.8045</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1419</v>
+        <v>0.6032</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3157</v>
+        <v>-1.4077</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.3814</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6974</v>
+        <v>0.9344</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0789</v>
+        <v>-1.3158</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-0.4231</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4445</v>
+        <v>-0.3311</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3947</v>
+        <v>-0.092</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4536</v>
+        <v>-0.3467</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4339</v>
+        <v>-0.2906</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0198</v>
+        <v>-0.0561</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ALVAREZ PUERTAS</t>
+          <t>J. TEJERA TEJO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.992</v>
+        <v>-0.982</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7766</v>
+        <v>-0.603</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2154</v>
+        <v>-0.3791</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8045</v>
+        <v>-1.4576</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6032</v>
+        <v>-1.1419</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4077</v>
+        <v>-0.3157</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3814</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9344</v>
+        <v>-0.6974</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3158</v>
+        <v>0.0789</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4231</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3311</v>
+        <v>-0.4445</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.092</v>
+        <v>-0.3947</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7687</v>
+        <v>0.0649</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3952</v>
+        <v>0.0155</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3734</v>
+        <v>0.0494</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1102</v>
+        <v>-2.4468</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.9742</v>
+        <v>-4.1834</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8639</v>
+        <v>1.7366</v>
       </c>
       <c r="G20" t="n">
         <v>-4.4365</v>
@@ -2014,13 +2014,13 @@
         <v>1.0267</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2441</v>
+        <v>0.9076</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3562</v>
+        <v>0.147</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8879</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>1.2875</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.4656</v>
+        <v>-5.7255</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.3252</v>
+        <v>-4.2206</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1405</v>
+        <v>-1.5049</v>
       </c>
       <c r="G21" t="n">
         <v>-4.0786</v>
@@ -2092,13 +2092,13 @@
         <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0298</v>
+        <v>-0.2896</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3411</v>
+        <v>-0.2365</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3114</v>
+        <v>-0.0531</v>
       </c>
       <c r="V21" t="n">
         <v>-1.7679</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.7135</v>
+        <v>-6.2776</v>
       </c>
       <c r="E22" t="n">
         <v>-5.6893</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0243</v>
+        <v>-0.5884</v>
       </c>
       <c r="G22" t="n">
         <v>-3.0832</v>
@@ -2170,13 +2170,13 @@
         <v>1.0267</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5851</v>
+        <v>-0.1492</v>
       </c>
       <c r="T22" t="n">
         <v>-0.07770000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5075</v>
+        <v>-0.0716</v>
       </c>
       <c r="V22" t="n">
         <v>0.2402</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.786799999999999</v>
+        <v>-5.3921</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.232099999999999</v>
+        <v>-9.232199999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>2.444999999999999</v>
+        <v>3.839799999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-7.287999999999998</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.433400000000001</v>
+        <v>-5.4334</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.854499999999999</v>
+        <v>-1.8545</v>
       </c>
       <c r="J23" t="n">
         <v>-1.5737</v>
@@ -2248,13 +2248,13 @@
         <v>12.3205</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0536</v>
+        <v>-0.6586</v>
       </c>
       <c r="T23" t="n">
         <v>-2.1712</v>
       </c>
       <c r="U23" t="n">
-        <v>0.118</v>
+        <v>1.5126</v>
       </c>
       <c r="V23" t="n">
         <v>1.5277</v>
